--- a/ig/test-tabs-svs/ValueSet-jdv-j373-type-autorite.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j373-type-autorite.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -128,7 +128,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite|20260330120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite|20260629120000</t>
   </si>
   <si>
     <t>version</t>
@@ -162,6 +162,30 @@
   </si>
   <si>
     <t>Conseil de l'Ordre</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Conseil départemental</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Direction Départementale de l'Emploi, du Travail et des Solidarités</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Direction régionale et interdépartementale de l'Hébergement et du Logement</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Directions régionales de l'économie de l'emploi du travail et des solidarités</t>
   </si>
   <si>
     <t>08</t>
@@ -523,7 +547,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -633,6 +657,90 @@
         <v>15</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
